--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135711669</v>
       </c>
       <c r="B2" t="n">
-        <v>87454</v>
+        <v>87455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135711638</v>
       </c>
       <c r="B3" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135711643</v>
       </c>
       <c r="B4" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>135711654</v>
       </c>
       <c r="B5" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135711659</v>
       </c>
       <c r="B6" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135711663</v>
       </c>
       <c r="B7" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>135711668</v>
       </c>
       <c r="B8" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135711688</v>
       </c>
       <c r="B9" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135711690</v>
       </c>
       <c r="B10" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>135711630</v>
       </c>
       <c r="B11" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>135711699</v>
       </c>
       <c r="B12" t="n">
-        <v>89290</v>
+        <v>89292</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135711701</v>
       </c>
       <c r="B13" t="n">
-        <v>89290</v>
+        <v>89292</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>135711697</v>
       </c>
       <c r="B14" t="n">
-        <v>93017</v>
+        <v>93019</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135711633</v>
       </c>
       <c r="B19" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>135711647</v>
       </c>
       <c r="B20" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135711631</v>
       </c>
       <c r="B21" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135711649</v>
       </c>
       <c r="B22" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>135711653</v>
       </c>
       <c r="B23" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>135711675</v>
       </c>
       <c r="B24" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135711691</v>
       </c>
       <c r="B25" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>135711708</v>
       </c>
       <c r="B26" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>135711709</v>
       </c>
       <c r="B27" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>135711634</v>
       </c>
       <c r="B28" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>135711636</v>
       </c>
       <c r="B29" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135711637</v>
       </c>
       <c r="B30" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>135711644</v>
       </c>
       <c r="B31" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>135711656</v>
       </c>
       <c r="B32" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>135711661</v>
       </c>
       <c r="B33" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>135711666</v>
       </c>
       <c r="B34" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>135711670</v>
       </c>
       <c r="B35" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>135711676</v>
       </c>
       <c r="B36" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135711677</v>
       </c>
       <c r="B37" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135711678</v>
       </c>
       <c r="B38" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135711679</v>
       </c>
       <c r="B39" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>135711680</v>
       </c>
       <c r="B40" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>135711681</v>
       </c>
       <c r="B41" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>135711682</v>
       </c>
       <c r="B42" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>135711685</v>
       </c>
       <c r="B43" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>135711692</v>
       </c>
       <c r="B44" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>135711693</v>
       </c>
       <c r="B45" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>135711698</v>
       </c>
       <c r="B46" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>135711700</v>
       </c>
       <c r="B47" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135711702</v>
       </c>
       <c r="B48" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>135711707</v>
       </c>
       <c r="B49" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>135711640</v>
       </c>
       <c r="B50" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>135711657</v>
       </c>
       <c r="B51" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>135711683</v>
       </c>
       <c r="B52" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>135711705</v>
       </c>
       <c r="B53" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>135711639</v>
       </c>
       <c r="B54" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>135711641</v>
       </c>
       <c r="B55" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>135711642</v>
       </c>
       <c r="B56" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>135711646</v>
       </c>
       <c r="B57" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>135711648</v>
       </c>
       <c r="B58" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>135711650</v>
       </c>
       <c r="B59" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>135711660</v>
       </c>
       <c r="B60" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>135711664</v>
       </c>
       <c r="B61" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>135711674</v>
       </c>
       <c r="B62" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>135711694</v>
       </c>
       <c r="B63" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>135711695</v>
       </c>
       <c r="B64" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>135711696</v>
       </c>
       <c r="B65" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>135711711</v>
       </c>
       <c r="B66" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>135711645</v>
       </c>
       <c r="B67" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>135711652</v>
       </c>
       <c r="B68" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135711689</v>
       </c>
       <c r="B69" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>135711651</v>
       </c>
       <c r="B70" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>135711684</v>
       </c>
       <c r="B71" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135711669</v>
       </c>
       <c r="B2" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135711638</v>
       </c>
       <c r="B3" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135711643</v>
       </c>
       <c r="B4" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>135711654</v>
       </c>
       <c r="B5" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135711659</v>
       </c>
       <c r="B6" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135711663</v>
       </c>
       <c r="B7" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>135711668</v>
       </c>
       <c r="B8" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135711688</v>
       </c>
       <c r="B9" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135711690</v>
       </c>
       <c r="B10" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>135711630</v>
       </c>
       <c r="B11" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>135711699</v>
       </c>
       <c r="B12" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135711701</v>
       </c>
       <c r="B13" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>135711697</v>
       </c>
       <c r="B14" t="n">
-        <v>93019</v>
+        <v>93034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135711658</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>135711703</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135711704</v>
       </c>
       <c r="B17" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135711686</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135711633</v>
       </c>
       <c r="B19" t="n">
-        <v>108294</v>
+        <v>108317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>135711647</v>
       </c>
       <c r="B20" t="n">
-        <v>108294</v>
+        <v>108317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135711631</v>
       </c>
       <c r="B21" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135711649</v>
       </c>
       <c r="B22" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>135711653</v>
       </c>
       <c r="B23" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>135711675</v>
       </c>
       <c r="B24" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135711691</v>
       </c>
       <c r="B25" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>135711708</v>
       </c>
       <c r="B26" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>135711709</v>
       </c>
       <c r="B27" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>135711634</v>
       </c>
       <c r="B28" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>135711636</v>
       </c>
       <c r="B29" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135711637</v>
       </c>
       <c r="B30" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>135711644</v>
       </c>
       <c r="B31" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>135711656</v>
       </c>
       <c r="B32" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>135711661</v>
       </c>
       <c r="B33" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>135711666</v>
       </c>
       <c r="B34" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>135711670</v>
       </c>
       <c r="B35" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>135711676</v>
       </c>
       <c r="B36" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135711677</v>
       </c>
       <c r="B37" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135711678</v>
       </c>
       <c r="B38" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135711679</v>
       </c>
       <c r="B39" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>135711680</v>
       </c>
       <c r="B40" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>135711681</v>
       </c>
       <c r="B41" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>135711682</v>
       </c>
       <c r="B42" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>135711685</v>
       </c>
       <c r="B43" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>135711692</v>
       </c>
       <c r="B44" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>135711693</v>
       </c>
       <c r="B45" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>135711698</v>
       </c>
       <c r="B46" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>135711700</v>
       </c>
       <c r="B47" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135711702</v>
       </c>
       <c r="B48" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>135711707</v>
       </c>
       <c r="B49" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>135711640</v>
       </c>
       <c r="B50" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>135711657</v>
       </c>
       <c r="B51" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>135711683</v>
       </c>
       <c r="B52" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>135711705</v>
       </c>
       <c r="B53" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>135711639</v>
       </c>
       <c r="B54" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>135711641</v>
       </c>
       <c r="B55" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>135711642</v>
       </c>
       <c r="B56" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>135711646</v>
       </c>
       <c r="B57" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>135711648</v>
       </c>
       <c r="B58" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>135711650</v>
       </c>
       <c r="B59" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>135711660</v>
       </c>
       <c r="B60" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>135711664</v>
       </c>
       <c r="B61" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>135711674</v>
       </c>
       <c r="B62" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>135711694</v>
       </c>
       <c r="B63" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>135711695</v>
       </c>
       <c r="B64" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>135711696</v>
       </c>
       <c r="B65" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>135711711</v>
       </c>
       <c r="B66" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>135711645</v>
       </c>
       <c r="B67" t="n">
-        <v>100888</v>
+        <v>100905</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>135711652</v>
       </c>
       <c r="B68" t="n">
-        <v>100888</v>
+        <v>100905</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135711689</v>
       </c>
       <c r="B69" t="n">
-        <v>100888</v>
+        <v>100905</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>135711651</v>
       </c>
       <c r="B70" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>135711684</v>
       </c>
       <c r="B71" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135711669</v>
       </c>
       <c r="B2" t="n">
-        <v>87457</v>
+        <v>87458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135711638</v>
       </c>
       <c r="B3" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135711643</v>
       </c>
       <c r="B4" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>135711654</v>
       </c>
       <c r="B5" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135711659</v>
       </c>
       <c r="B6" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135711663</v>
       </c>
       <c r="B7" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>135711668</v>
       </c>
       <c r="B8" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135711688</v>
       </c>
       <c r="B9" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135711690</v>
       </c>
       <c r="B10" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>135711630</v>
       </c>
       <c r="B11" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>135711699</v>
       </c>
       <c r="B12" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135711701</v>
       </c>
       <c r="B13" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>135711697</v>
       </c>
       <c r="B14" t="n">
-        <v>93034</v>
+        <v>93035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135711658</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>135711703</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135711704</v>
       </c>
       <c r="B17" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135711633</v>
       </c>
       <c r="B19" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>135711647</v>
       </c>
       <c r="B20" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135711631</v>
       </c>
       <c r="B21" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135711649</v>
       </c>
       <c r="B22" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>135711653</v>
       </c>
       <c r="B23" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>135711675</v>
       </c>
       <c r="B24" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135711691</v>
       </c>
       <c r="B25" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>135711708</v>
       </c>
       <c r="B26" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>135711709</v>
       </c>
       <c r="B27" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>135711634</v>
       </c>
       <c r="B28" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>135711636</v>
       </c>
       <c r="B29" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135711637</v>
       </c>
       <c r="B30" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>135711644</v>
       </c>
       <c r="B31" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>135711656</v>
       </c>
       <c r="B32" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>135711661</v>
       </c>
       <c r="B33" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>135711666</v>
       </c>
       <c r="B34" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>135711670</v>
       </c>
       <c r="B35" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>135711676</v>
       </c>
       <c r="B36" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135711677</v>
       </c>
       <c r="B37" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135711678</v>
       </c>
       <c r="B38" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135711679</v>
       </c>
       <c r="B39" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>135711680</v>
       </c>
       <c r="B40" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>135711681</v>
       </c>
       <c r="B41" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>135711682</v>
       </c>
       <c r="B42" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>135711685</v>
       </c>
       <c r="B43" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>135711692</v>
       </c>
       <c r="B44" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>135711693</v>
       </c>
       <c r="B45" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>135711698</v>
       </c>
       <c r="B46" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>135711700</v>
       </c>
       <c r="B47" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135711702</v>
       </c>
       <c r="B48" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>135711707</v>
       </c>
       <c r="B49" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>135711640</v>
       </c>
       <c r="B50" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>135711657</v>
       </c>
       <c r="B51" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>135711683</v>
       </c>
       <c r="B52" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>135711705</v>
       </c>
       <c r="B53" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>135711639</v>
       </c>
       <c r="B54" t="n">
-        <v>104815</v>
+        <v>104817</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>135711641</v>
       </c>
       <c r="B55" t="n">
-        <v>104815</v>
+        <v>104817</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>135711642</v>
       </c>
       <c r="B56" t="n">
-        <v>104815</v>
+        <v>104817</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>135711646</v>
       </c>
       <c r="B57" t="n">
-        <v>104815</v>
+        <v>104817</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>135711648</v>
       </c>
       <c r="B58" t="n">
-        <v>104815</v>
+        <v>104817</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>135711650</v>
       </c>
       <c r="B59" t="n">
-        <v>104815</v>
+        <v>104817</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>135711660</v>
       </c>
       <c r="B60" t="n">
-        <v>104815</v>
+        <v>104817</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>135711664</v>
       </c>
       <c r="B61" t="n">
-        <v>104815</v>
+        <v>104817</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>135711674</v>
       </c>
       <c r="B62" t="n">
-        <v>104815</v>
+        <v>104817</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>135711694</v>
       </c>
       <c r="B63" t="n">
-        <v>104815</v>
+        <v>104817</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>135711695</v>
       </c>
       <c r="B64" t="n">
-        <v>104815</v>
+        <v>104817</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>135711696</v>
       </c>
       <c r="B65" t="n">
-        <v>104815</v>
+        <v>104817</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>135711711</v>
       </c>
       <c r="B66" t="n">
-        <v>104815</v>
+        <v>104817</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>135711645</v>
       </c>
       <c r="B67" t="n">
-        <v>100905</v>
+        <v>100907</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>135711652</v>
       </c>
       <c r="B68" t="n">
-        <v>100905</v>
+        <v>100907</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135711689</v>
       </c>
       <c r="B69" t="n">
-        <v>100905</v>
+        <v>100907</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>135711651</v>
       </c>
       <c r="B70" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>135711684</v>
       </c>
       <c r="B71" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135711669</v>
       </c>
       <c r="B2" t="n">
-        <v>87458</v>
+        <v>87459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135711638</v>
       </c>
       <c r="B3" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135711643</v>
       </c>
       <c r="B4" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>135711654</v>
       </c>
       <c r="B5" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135711659</v>
       </c>
       <c r="B6" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135711663</v>
       </c>
       <c r="B7" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>135711668</v>
       </c>
       <c r="B8" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135711688</v>
       </c>
       <c r="B9" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135711690</v>
       </c>
       <c r="B10" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>135711630</v>
       </c>
       <c r="B11" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>135711699</v>
       </c>
       <c r="B12" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135711701</v>
       </c>
       <c r="B13" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>135711697</v>
       </c>
       <c r="B14" t="n">
-        <v>93035</v>
+        <v>93036</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135711633</v>
       </c>
       <c r="B19" t="n">
-        <v>108319</v>
+        <v>108320</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>135711647</v>
       </c>
       <c r="B20" t="n">
-        <v>108319</v>
+        <v>108320</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135711631</v>
       </c>
       <c r="B21" t="n">
-        <v>108389</v>
+        <v>108390</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135711649</v>
       </c>
       <c r="B22" t="n">
-        <v>108389</v>
+        <v>108390</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>135711653</v>
       </c>
       <c r="B23" t="n">
-        <v>108389</v>
+        <v>108390</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>135711675</v>
       </c>
       <c r="B24" t="n">
-        <v>108389</v>
+        <v>108390</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135711691</v>
       </c>
       <c r="B25" t="n">
-        <v>108389</v>
+        <v>108390</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>135711708</v>
       </c>
       <c r="B26" t="n">
-        <v>108389</v>
+        <v>108390</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>135711709</v>
       </c>
       <c r="B27" t="n">
-        <v>108389</v>
+        <v>108390</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>135711634</v>
       </c>
       <c r="B28" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>135711636</v>
       </c>
       <c r="B29" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135711637</v>
       </c>
       <c r="B30" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>135711644</v>
       </c>
       <c r="B31" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>135711656</v>
       </c>
       <c r="B32" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>135711661</v>
       </c>
       <c r="B33" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>135711666</v>
       </c>
       <c r="B34" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>135711670</v>
       </c>
       <c r="B35" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>135711676</v>
       </c>
       <c r="B36" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135711677</v>
       </c>
       <c r="B37" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135711678</v>
       </c>
       <c r="B38" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135711679</v>
       </c>
       <c r="B39" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>135711680</v>
       </c>
       <c r="B40" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>135711681</v>
       </c>
       <c r="B41" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>135711682</v>
       </c>
       <c r="B42" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>135711685</v>
       </c>
       <c r="B43" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>135711692</v>
       </c>
       <c r="B44" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>135711693</v>
       </c>
       <c r="B45" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>135711698</v>
       </c>
       <c r="B46" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>135711700</v>
       </c>
       <c r="B47" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135711702</v>
       </c>
       <c r="B48" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>135711707</v>
       </c>
       <c r="B49" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>135711640</v>
       </c>
       <c r="B50" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>135711657</v>
       </c>
       <c r="B51" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>135711683</v>
       </c>
       <c r="B52" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>135711705</v>
       </c>
       <c r="B53" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>135711639</v>
       </c>
       <c r="B54" t="n">
-        <v>104817</v>
+        <v>104818</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>135711641</v>
       </c>
       <c r="B55" t="n">
-        <v>104817</v>
+        <v>104818</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>135711642</v>
       </c>
       <c r="B56" t="n">
-        <v>104817</v>
+        <v>104818</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>135711646</v>
       </c>
       <c r="B57" t="n">
-        <v>104817</v>
+        <v>104818</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>135711648</v>
       </c>
       <c r="B58" t="n">
-        <v>104817</v>
+        <v>104818</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>135711650</v>
       </c>
       <c r="B59" t="n">
-        <v>104817</v>
+        <v>104818</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>135711660</v>
       </c>
       <c r="B60" t="n">
-        <v>104817</v>
+        <v>104818</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>135711664</v>
       </c>
       <c r="B61" t="n">
-        <v>104817</v>
+        <v>104818</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>135711674</v>
       </c>
       <c r="B62" t="n">
-        <v>104817</v>
+        <v>104818</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>135711694</v>
       </c>
       <c r="B63" t="n">
-        <v>104817</v>
+        <v>104818</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>135711695</v>
       </c>
       <c r="B64" t="n">
-        <v>104817</v>
+        <v>104818</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>135711696</v>
       </c>
       <c r="B65" t="n">
-        <v>104817</v>
+        <v>104818</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>135711711</v>
       </c>
       <c r="B66" t="n">
-        <v>104817</v>
+        <v>104818</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>135711645</v>
       </c>
       <c r="B67" t="n">
-        <v>100907</v>
+        <v>100908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>135711652</v>
       </c>
       <c r="B68" t="n">
-        <v>100907</v>
+        <v>100908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135711689</v>
       </c>
       <c r="B69" t="n">
-        <v>100907</v>
+        <v>100908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>135711651</v>
       </c>
       <c r="B70" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>135711684</v>
       </c>
       <c r="B71" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135711669</v>
       </c>
       <c r="B2" t="n">
-        <v>87459</v>
+        <v>87460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135711638</v>
       </c>
       <c r="B3" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135711643</v>
       </c>
       <c r="B4" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>135711654</v>
       </c>
       <c r="B5" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135711659</v>
       </c>
       <c r="B6" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135711663</v>
       </c>
       <c r="B7" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>135711668</v>
       </c>
       <c r="B8" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135711688</v>
       </c>
       <c r="B9" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135711690</v>
       </c>
       <c r="B10" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>135711630</v>
       </c>
       <c r="B11" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>135711699</v>
       </c>
       <c r="B12" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135711701</v>
       </c>
       <c r="B13" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>135711697</v>
       </c>
       <c r="B14" t="n">
-        <v>93036</v>
+        <v>93037</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135711658</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>135711703</v>
       </c>
       <c r="B16" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135711704</v>
       </c>
       <c r="B17" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135711686</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135711633</v>
       </c>
       <c r="B19" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>135711647</v>
       </c>
       <c r="B20" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135711631</v>
       </c>
       <c r="B21" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135711649</v>
       </c>
       <c r="B22" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>135711653</v>
       </c>
       <c r="B23" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>135711675</v>
       </c>
       <c r="B24" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135711691</v>
       </c>
       <c r="B25" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>135711708</v>
       </c>
       <c r="B26" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>135711709</v>
       </c>
       <c r="B27" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>135711634</v>
       </c>
       <c r="B28" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>135711636</v>
       </c>
       <c r="B29" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135711637</v>
       </c>
       <c r="B30" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>135711644</v>
       </c>
       <c r="B31" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>135711656</v>
       </c>
       <c r="B32" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>135711661</v>
       </c>
       <c r="B33" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>135711666</v>
       </c>
       <c r="B34" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>135711670</v>
       </c>
       <c r="B35" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>135711676</v>
       </c>
       <c r="B36" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135711677</v>
       </c>
       <c r="B37" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135711678</v>
       </c>
       <c r="B38" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135711679</v>
       </c>
       <c r="B39" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>135711680</v>
       </c>
       <c r="B40" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>135711681</v>
       </c>
       <c r="B41" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>135711682</v>
       </c>
       <c r="B42" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>135711685</v>
       </c>
       <c r="B43" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>135711692</v>
       </c>
       <c r="B44" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>135711693</v>
       </c>
       <c r="B45" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>135711698</v>
       </c>
       <c r="B46" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>135711700</v>
       </c>
       <c r="B47" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135711702</v>
       </c>
       <c r="B48" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>135711707</v>
       </c>
       <c r="B49" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>135711640</v>
       </c>
       <c r="B50" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>135711657</v>
       </c>
       <c r="B51" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>135711683</v>
       </c>
       <c r="B52" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>135711705</v>
       </c>
       <c r="B53" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>135711639</v>
       </c>
       <c r="B54" t="n">
-        <v>104818</v>
+        <v>104819</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>135711641</v>
       </c>
       <c r="B55" t="n">
-        <v>104818</v>
+        <v>104819</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>135711642</v>
       </c>
       <c r="B56" t="n">
-        <v>104818</v>
+        <v>104819</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>135711646</v>
       </c>
       <c r="B57" t="n">
-        <v>104818</v>
+        <v>104819</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>135711648</v>
       </c>
       <c r="B58" t="n">
-        <v>104818</v>
+        <v>104819</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>135711650</v>
       </c>
       <c r="B59" t="n">
-        <v>104818</v>
+        <v>104819</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>135711660</v>
       </c>
       <c r="B60" t="n">
-        <v>104818</v>
+        <v>104819</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>135711664</v>
       </c>
       <c r="B61" t="n">
-        <v>104818</v>
+        <v>104819</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>135711674</v>
       </c>
       <c r="B62" t="n">
-        <v>104818</v>
+        <v>104819</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>135711694</v>
       </c>
       <c r="B63" t="n">
-        <v>104818</v>
+        <v>104819</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>135711695</v>
       </c>
       <c r="B64" t="n">
-        <v>104818</v>
+        <v>104819</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>135711696</v>
       </c>
       <c r="B65" t="n">
-        <v>104818</v>
+        <v>104819</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>135711711</v>
       </c>
       <c r="B66" t="n">
-        <v>104818</v>
+        <v>104819</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>135711645</v>
       </c>
       <c r="B67" t="n">
-        <v>100908</v>
+        <v>100909</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>135711652</v>
       </c>
       <c r="B68" t="n">
-        <v>100908</v>
+        <v>100909</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135711689</v>
       </c>
       <c r="B69" t="n">
-        <v>100908</v>
+        <v>100909</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>135711651</v>
       </c>
       <c r="B70" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>135711684</v>
       </c>
       <c r="B71" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135711669</v>
       </c>
       <c r="B2" t="n">
-        <v>87460</v>
+        <v>87466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135711638</v>
       </c>
       <c r="B3" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135711643</v>
       </c>
       <c r="B4" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>135711654</v>
       </c>
       <c r="B5" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135711659</v>
       </c>
       <c r="B6" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135711663</v>
       </c>
       <c r="B7" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>135711668</v>
       </c>
       <c r="B8" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135711688</v>
       </c>
       <c r="B9" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135711690</v>
       </c>
       <c r="B10" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>135711630</v>
       </c>
       <c r="B11" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>135711699</v>
       </c>
       <c r="B12" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135711701</v>
       </c>
       <c r="B13" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>135711697</v>
       </c>
       <c r="B14" t="n">
-        <v>93037</v>
+        <v>93043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135711658</v>
       </c>
       <c r="B15" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>135711703</v>
       </c>
       <c r="B16" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135711704</v>
       </c>
       <c r="B17" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135711686</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135711633</v>
       </c>
       <c r="B19" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>135711647</v>
       </c>
       <c r="B20" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135711631</v>
       </c>
       <c r="B21" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135711649</v>
       </c>
       <c r="B22" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>135711653</v>
       </c>
       <c r="B23" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>135711675</v>
       </c>
       <c r="B24" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135711691</v>
       </c>
       <c r="B25" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>135711708</v>
       </c>
       <c r="B26" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>135711709</v>
       </c>
       <c r="B27" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>135711634</v>
       </c>
       <c r="B28" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>135711636</v>
       </c>
       <c r="B29" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135711637</v>
       </c>
       <c r="B30" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>135711644</v>
       </c>
       <c r="B31" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>135711656</v>
       </c>
       <c r="B32" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>135711661</v>
       </c>
       <c r="B33" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>135711666</v>
       </c>
       <c r="B34" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>135711670</v>
       </c>
       <c r="B35" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>135711676</v>
       </c>
       <c r="B36" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135711677</v>
       </c>
       <c r="B37" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135711678</v>
       </c>
       <c r="B38" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135711679</v>
       </c>
       <c r="B39" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>135711680</v>
       </c>
       <c r="B40" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>135711681</v>
       </c>
       <c r="B41" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>135711682</v>
       </c>
       <c r="B42" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>135711685</v>
       </c>
       <c r="B43" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>135711692</v>
       </c>
       <c r="B44" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>135711693</v>
       </c>
       <c r="B45" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>135711698</v>
       </c>
       <c r="B46" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>135711700</v>
       </c>
       <c r="B47" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135711702</v>
       </c>
       <c r="B48" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>135711707</v>
       </c>
       <c r="B49" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>135711640</v>
       </c>
       <c r="B50" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>135711657</v>
       </c>
       <c r="B51" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>135711683</v>
       </c>
       <c r="B52" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>135711705</v>
       </c>
       <c r="B53" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>135711639</v>
       </c>
       <c r="B54" t="n">
-        <v>104819</v>
+        <v>104825</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>135711641</v>
       </c>
       <c r="B55" t="n">
-        <v>104819</v>
+        <v>104825</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>135711642</v>
       </c>
       <c r="B56" t="n">
-        <v>104819</v>
+        <v>104825</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>135711646</v>
       </c>
       <c r="B57" t="n">
-        <v>104819</v>
+        <v>104825</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>135711648</v>
       </c>
       <c r="B58" t="n">
-        <v>104819</v>
+        <v>104825</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>135711650</v>
       </c>
       <c r="B59" t="n">
-        <v>104819</v>
+        <v>104825</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>135711660</v>
       </c>
       <c r="B60" t="n">
-        <v>104819</v>
+        <v>104825</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>135711664</v>
       </c>
       <c r="B61" t="n">
-        <v>104819</v>
+        <v>104825</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>135711674</v>
       </c>
       <c r="B62" t="n">
-        <v>104819</v>
+        <v>104825</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>135711694</v>
       </c>
       <c r="B63" t="n">
-        <v>104819</v>
+        <v>104825</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>135711695</v>
       </c>
       <c r="B64" t="n">
-        <v>104819</v>
+        <v>104825</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>135711696</v>
       </c>
       <c r="B65" t="n">
-        <v>104819</v>
+        <v>104825</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>135711711</v>
       </c>
       <c r="B66" t="n">
-        <v>104819</v>
+        <v>104825</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>135711645</v>
       </c>
       <c r="B67" t="n">
-        <v>100909</v>
+        <v>100915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>135711652</v>
       </c>
       <c r="B68" t="n">
-        <v>100909</v>
+        <v>100915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135711689</v>
       </c>
       <c r="B69" t="n">
-        <v>100909</v>
+        <v>100915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>135711651</v>
       </c>
       <c r="B70" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>135711684</v>
       </c>
       <c r="B71" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135711669</v>
       </c>
       <c r="B2" t="n">
-        <v>87466</v>
+        <v>87467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135711638</v>
       </c>
       <c r="B3" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135711643</v>
       </c>
       <c r="B4" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>135711654</v>
       </c>
       <c r="B5" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135711659</v>
       </c>
       <c r="B6" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135711663</v>
       </c>
       <c r="B7" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>135711668</v>
       </c>
       <c r="B8" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135711688</v>
       </c>
       <c r="B9" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135711690</v>
       </c>
       <c r="B10" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>135711630</v>
       </c>
       <c r="B11" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>135711699</v>
       </c>
       <c r="B12" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135711701</v>
       </c>
       <c r="B13" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>135711697</v>
       </c>
       <c r="B14" t="n">
-        <v>93043</v>
+        <v>93044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135711658</v>
       </c>
       <c r="B15" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>135711703</v>
       </c>
       <c r="B16" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135711704</v>
       </c>
       <c r="B17" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135711686</v>
       </c>
       <c r="B18" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135711633</v>
       </c>
       <c r="B19" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>135711647</v>
       </c>
       <c r="B20" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135711631</v>
       </c>
       <c r="B21" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135711649</v>
       </c>
       <c r="B22" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>135711653</v>
       </c>
       <c r="B23" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>135711675</v>
       </c>
       <c r="B24" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135711691</v>
       </c>
       <c r="B25" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>135711708</v>
       </c>
       <c r="B26" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>135711709</v>
       </c>
       <c r="B27" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>135711634</v>
       </c>
       <c r="B28" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>135711636</v>
       </c>
       <c r="B29" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135711637</v>
       </c>
       <c r="B30" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>135711644</v>
       </c>
       <c r="B31" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>135711656</v>
       </c>
       <c r="B32" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>135711661</v>
       </c>
       <c r="B33" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>135711666</v>
       </c>
       <c r="B34" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>135711670</v>
       </c>
       <c r="B35" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>135711676</v>
       </c>
       <c r="B36" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135711677</v>
       </c>
       <c r="B37" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135711678</v>
       </c>
       <c r="B38" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135711679</v>
       </c>
       <c r="B39" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>135711680</v>
       </c>
       <c r="B40" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>135711681</v>
       </c>
       <c r="B41" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>135711682</v>
       </c>
       <c r="B42" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>135711685</v>
       </c>
       <c r="B43" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>135711692</v>
       </c>
       <c r="B44" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>135711693</v>
       </c>
       <c r="B45" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>135711698</v>
       </c>
       <c r="B46" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>135711700</v>
       </c>
       <c r="B47" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135711702</v>
       </c>
       <c r="B48" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>135711707</v>
       </c>
       <c r="B49" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>135711640</v>
       </c>
       <c r="B50" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>135711657</v>
       </c>
       <c r="B51" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>135711683</v>
       </c>
       <c r="B52" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>135711705</v>
       </c>
       <c r="B53" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>135711639</v>
       </c>
       <c r="B54" t="n">
-        <v>104825</v>
+        <v>104826</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>135711641</v>
       </c>
       <c r="B55" t="n">
-        <v>104825</v>
+        <v>104826</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>135711642</v>
       </c>
       <c r="B56" t="n">
-        <v>104825</v>
+        <v>104826</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>135711646</v>
       </c>
       <c r="B57" t="n">
-        <v>104825</v>
+        <v>104826</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>135711648</v>
       </c>
       <c r="B58" t="n">
-        <v>104825</v>
+        <v>104826</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>135711650</v>
       </c>
       <c r="B59" t="n">
-        <v>104825</v>
+        <v>104826</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>135711660</v>
       </c>
       <c r="B60" t="n">
-        <v>104825</v>
+        <v>104826</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>135711664</v>
       </c>
       <c r="B61" t="n">
-        <v>104825</v>
+        <v>104826</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>135711674</v>
       </c>
       <c r="B62" t="n">
-        <v>104825</v>
+        <v>104826</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>135711694</v>
       </c>
       <c r="B63" t="n">
-        <v>104825</v>
+        <v>104826</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>135711695</v>
       </c>
       <c r="B64" t="n">
-        <v>104825</v>
+        <v>104826</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>135711696</v>
       </c>
       <c r="B65" t="n">
-        <v>104825</v>
+        <v>104826</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>135711711</v>
       </c>
       <c r="B66" t="n">
-        <v>104825</v>
+        <v>104826</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>135711645</v>
       </c>
       <c r="B67" t="n">
-        <v>100915</v>
+        <v>100916</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>135711652</v>
       </c>
       <c r="B68" t="n">
-        <v>100915</v>
+        <v>100916</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135711689</v>
       </c>
       <c r="B69" t="n">
-        <v>100915</v>
+        <v>100916</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>135711651</v>
       </c>
       <c r="B70" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>135711684</v>
       </c>
       <c r="B71" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135711669</v>
       </c>
       <c r="B2" t="n">
-        <v>87467</v>
+        <v>87473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135711638</v>
       </c>
       <c r="B3" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135711643</v>
       </c>
       <c r="B4" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>135711654</v>
       </c>
       <c r="B5" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135711659</v>
       </c>
       <c r="B6" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135711663</v>
       </c>
       <c r="B7" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>135711668</v>
       </c>
       <c r="B8" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135711688</v>
       </c>
       <c r="B9" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135711690</v>
       </c>
       <c r="B10" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>135711630</v>
       </c>
       <c r="B11" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>135711699</v>
       </c>
       <c r="B12" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135711701</v>
       </c>
       <c r="B13" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>135711697</v>
       </c>
       <c r="B14" t="n">
-        <v>93044</v>
+        <v>93050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135711658</v>
       </c>
       <c r="B15" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>135711703</v>
       </c>
       <c r="B16" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135711704</v>
       </c>
       <c r="B17" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135711633</v>
       </c>
       <c r="B19" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>135711647</v>
       </c>
       <c r="B20" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135711631</v>
       </c>
       <c r="B21" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135711649</v>
       </c>
       <c r="B22" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>135711653</v>
       </c>
       <c r="B23" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>135711675</v>
       </c>
       <c r="B24" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135711691</v>
       </c>
       <c r="B25" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>135711708</v>
       </c>
       <c r="B26" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>135711709</v>
       </c>
       <c r="B27" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>135711634</v>
       </c>
       <c r="B28" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>135711636</v>
       </c>
       <c r="B29" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135711637</v>
       </c>
       <c r="B30" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>135711644</v>
       </c>
       <c r="B31" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>135711656</v>
       </c>
       <c r="B32" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>135711661</v>
       </c>
       <c r="B33" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>135711666</v>
       </c>
       <c r="B34" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>135711670</v>
       </c>
       <c r="B35" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>135711676</v>
       </c>
       <c r="B36" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135711677</v>
       </c>
       <c r="B37" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135711678</v>
       </c>
       <c r="B38" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135711679</v>
       </c>
       <c r="B39" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>135711680</v>
       </c>
       <c r="B40" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>135711681</v>
       </c>
       <c r="B41" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>135711682</v>
       </c>
       <c r="B42" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>135711685</v>
       </c>
       <c r="B43" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>135711692</v>
       </c>
       <c r="B44" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>135711693</v>
       </c>
       <c r="B45" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>135711698</v>
       </c>
       <c r="B46" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>135711700</v>
       </c>
       <c r="B47" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135711702</v>
       </c>
       <c r="B48" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>135711707</v>
       </c>
       <c r="B49" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>135711640</v>
       </c>
       <c r="B50" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>135711657</v>
       </c>
       <c r="B51" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>135711683</v>
       </c>
       <c r="B52" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>135711705</v>
       </c>
       <c r="B53" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>135711639</v>
       </c>
       <c r="B54" t="n">
-        <v>104826</v>
+        <v>104837</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>135711641</v>
       </c>
       <c r="B55" t="n">
-        <v>104826</v>
+        <v>104837</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>135711642</v>
       </c>
       <c r="B56" t="n">
-        <v>104826</v>
+        <v>104837</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>135711646</v>
       </c>
       <c r="B57" t="n">
-        <v>104826</v>
+        <v>104837</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>135711648</v>
       </c>
       <c r="B58" t="n">
-        <v>104826</v>
+        <v>104837</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>135711650</v>
       </c>
       <c r="B59" t="n">
-        <v>104826</v>
+        <v>104837</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>135711660</v>
       </c>
       <c r="B60" t="n">
-        <v>104826</v>
+        <v>104837</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>135711664</v>
       </c>
       <c r="B61" t="n">
-        <v>104826</v>
+        <v>104837</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>135711674</v>
       </c>
       <c r="B62" t="n">
-        <v>104826</v>
+        <v>104837</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>135711694</v>
       </c>
       <c r="B63" t="n">
-        <v>104826</v>
+        <v>104837</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>135711695</v>
       </c>
       <c r="B64" t="n">
-        <v>104826</v>
+        <v>104837</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>135711696</v>
       </c>
       <c r="B65" t="n">
-        <v>104826</v>
+        <v>104837</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>135711711</v>
       </c>
       <c r="B66" t="n">
-        <v>104826</v>
+        <v>104837</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>135711645</v>
       </c>
       <c r="B67" t="n">
-        <v>100916</v>
+        <v>100927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>135711652</v>
       </c>
       <c r="B68" t="n">
-        <v>100916</v>
+        <v>100927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135711689</v>
       </c>
       <c r="B69" t="n">
-        <v>100916</v>
+        <v>100927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>135711651</v>
       </c>
       <c r="B70" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>135711684</v>
       </c>
       <c r="B71" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135711669</v>
       </c>
       <c r="B2" t="n">
-        <v>87473</v>
+        <v>87480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135711638</v>
       </c>
       <c r="B3" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135711643</v>
       </c>
       <c r="B4" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>135711654</v>
       </c>
       <c r="B5" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135711659</v>
       </c>
       <c r="B6" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135711663</v>
       </c>
       <c r="B7" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>135711668</v>
       </c>
       <c r="B8" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135711688</v>
       </c>
       <c r="B9" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135711690</v>
       </c>
       <c r="B10" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>135711630</v>
       </c>
       <c r="B11" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>135711699</v>
       </c>
       <c r="B12" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135711701</v>
       </c>
       <c r="B13" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>135711697</v>
       </c>
       <c r="B14" t="n">
-        <v>93050</v>
+        <v>93057</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>135711658</v>
       </c>
       <c r="B15" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>135711703</v>
       </c>
       <c r="B16" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135711704</v>
       </c>
       <c r="B17" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135711686</v>
       </c>
       <c r="B18" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135711633</v>
       </c>
       <c r="B19" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>135711647</v>
       </c>
       <c r="B20" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135711631</v>
       </c>
       <c r="B21" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135711649</v>
       </c>
       <c r="B22" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>135711653</v>
       </c>
       <c r="B23" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>135711675</v>
       </c>
       <c r="B24" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135711691</v>
       </c>
       <c r="B25" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>135711708</v>
       </c>
       <c r="B26" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>135711709</v>
       </c>
       <c r="B27" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>135711634</v>
       </c>
       <c r="B28" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>135711636</v>
       </c>
       <c r="B29" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135711637</v>
       </c>
       <c r="B30" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>135711644</v>
       </c>
       <c r="B31" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>135711656</v>
       </c>
       <c r="B32" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>135711661</v>
       </c>
       <c r="B33" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>135711666</v>
       </c>
       <c r="B34" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>135711670</v>
       </c>
       <c r="B35" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>135711676</v>
       </c>
       <c r="B36" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135711677</v>
       </c>
       <c r="B37" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135711678</v>
       </c>
       <c r="B38" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135711679</v>
       </c>
       <c r="B39" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>135711680</v>
       </c>
       <c r="B40" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>135711681</v>
       </c>
       <c r="B41" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>135711682</v>
       </c>
       <c r="B42" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>135711685</v>
       </c>
       <c r="B43" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>135711692</v>
       </c>
       <c r="B44" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>135711693</v>
       </c>
       <c r="B45" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>135711698</v>
       </c>
       <c r="B46" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>135711700</v>
       </c>
       <c r="B47" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135711702</v>
       </c>
       <c r="B48" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>135711707</v>
       </c>
       <c r="B49" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>135711640</v>
       </c>
       <c r="B50" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>135711657</v>
       </c>
       <c r="B51" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>135711683</v>
       </c>
       <c r="B52" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>135711705</v>
       </c>
       <c r="B53" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>135711639</v>
       </c>
       <c r="B54" t="n">
-        <v>104837</v>
+        <v>104850</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>135711641</v>
       </c>
       <c r="B55" t="n">
-        <v>104837</v>
+        <v>104850</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>135711642</v>
       </c>
       <c r="B56" t="n">
-        <v>104837</v>
+        <v>104850</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>135711646</v>
       </c>
       <c r="B57" t="n">
-        <v>104837</v>
+        <v>104850</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>135711648</v>
       </c>
       <c r="B58" t="n">
-        <v>104837</v>
+        <v>104850</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>135711650</v>
       </c>
       <c r="B59" t="n">
-        <v>104837</v>
+        <v>104850</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>135711660</v>
       </c>
       <c r="B60" t="n">
-        <v>104837</v>
+        <v>104850</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>135711664</v>
       </c>
       <c r="B61" t="n">
-        <v>104837</v>
+        <v>104850</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>135711674</v>
       </c>
       <c r="B62" t="n">
-        <v>104837</v>
+        <v>104850</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>135711694</v>
       </c>
       <c r="B63" t="n">
-        <v>104837</v>
+        <v>104850</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>135711695</v>
       </c>
       <c r="B64" t="n">
-        <v>104837</v>
+        <v>104850</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>135711696</v>
       </c>
       <c r="B65" t="n">
-        <v>104837</v>
+        <v>104850</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>135711711</v>
       </c>
       <c r="B66" t="n">
-        <v>104837</v>
+        <v>104850</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>135711645</v>
       </c>
       <c r="B67" t="n">
-        <v>100927</v>
+        <v>100940</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>135711652</v>
       </c>
       <c r="B68" t="n">
-        <v>100927</v>
+        <v>100940</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135711689</v>
       </c>
       <c r="B69" t="n">
-        <v>100927</v>
+        <v>100940</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>135711651</v>
       </c>
       <c r="B70" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>135711684</v>
       </c>
       <c r="B71" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135711638</v>
       </c>
       <c r="B3" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135711643</v>
       </c>
       <c r="B4" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>135711654</v>
       </c>
       <c r="B5" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135711659</v>
       </c>
       <c r="B6" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135711663</v>
       </c>
       <c r="B7" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>135711668</v>
       </c>
       <c r="B8" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135711688</v>
       </c>
       <c r="B9" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135711690</v>
       </c>
       <c r="B10" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>135711630</v>
       </c>
       <c r="B11" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>135711699</v>
       </c>
       <c r="B12" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135711701</v>
       </c>
       <c r="B13" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>135711697</v>
       </c>
       <c r="B14" t="n">
-        <v>93057</v>
+        <v>93058</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135711633</v>
       </c>
       <c r="B19" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>135711647</v>
       </c>
       <c r="B20" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>135711631</v>
       </c>
       <c r="B21" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>135711649</v>
       </c>
       <c r="B22" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>135711653</v>
       </c>
       <c r="B23" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>135711675</v>
       </c>
       <c r="B24" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135711691</v>
       </c>
       <c r="B25" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>135711708</v>
       </c>
       <c r="B26" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>135711709</v>
       </c>
       <c r="B27" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>135711634</v>
       </c>
       <c r="B28" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>135711636</v>
       </c>
       <c r="B29" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135711637</v>
       </c>
       <c r="B30" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>135711644</v>
       </c>
       <c r="B31" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>135711656</v>
       </c>
       <c r="B32" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>135711661</v>
       </c>
       <c r="B33" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>135711666</v>
       </c>
       <c r="B34" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>135711670</v>
       </c>
       <c r="B35" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>135711676</v>
       </c>
       <c r="B36" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>135711677</v>
       </c>
       <c r="B37" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>135711678</v>
       </c>
       <c r="B38" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>135711679</v>
       </c>
       <c r="B39" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>135711680</v>
       </c>
       <c r="B40" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>135711681</v>
       </c>
       <c r="B41" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>135711682</v>
       </c>
       <c r="B42" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>135711685</v>
       </c>
       <c r="B43" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>135711692</v>
       </c>
       <c r="B44" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>135711693</v>
       </c>
       <c r="B45" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>135711698</v>
       </c>
       <c r="B46" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>135711700</v>
       </c>
       <c r="B47" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135711702</v>
       </c>
       <c r="B48" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>135711707</v>
       </c>
       <c r="B49" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>135711640</v>
       </c>
       <c r="B50" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>135711657</v>
       </c>
       <c r="B51" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>135711683</v>
       </c>
       <c r="B52" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>135711705</v>
       </c>
       <c r="B53" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>135711639</v>
       </c>
       <c r="B54" t="n">
-        <v>104850</v>
+        <v>104851</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>135711641</v>
       </c>
       <c r="B55" t="n">
-        <v>104850</v>
+        <v>104851</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>135711642</v>
       </c>
       <c r="B56" t="n">
-        <v>104850</v>
+        <v>104851</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>135711646</v>
       </c>
       <c r="B57" t="n">
-        <v>104850</v>
+        <v>104851</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>135711648</v>
       </c>
       <c r="B58" t="n">
-        <v>104850</v>
+        <v>104851</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>135711650</v>
       </c>
       <c r="B59" t="n">
-        <v>104850</v>
+        <v>104851</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>135711660</v>
       </c>
       <c r="B60" t="n">
-        <v>104850</v>
+        <v>104851</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>135711664</v>
       </c>
       <c r="B61" t="n">
-        <v>104850</v>
+        <v>104851</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>135711674</v>
       </c>
       <c r="B62" t="n">
-        <v>104850</v>
+        <v>104851</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>135711694</v>
       </c>
       <c r="B63" t="n">
-        <v>104850</v>
+        <v>104851</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>135711695</v>
       </c>
       <c r="B64" t="n">
-        <v>104850</v>
+        <v>104851</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>135711696</v>
       </c>
       <c r="B65" t="n">
-        <v>104850</v>
+        <v>104851</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>135711711</v>
       </c>
       <c r="B66" t="n">
-        <v>104850</v>
+        <v>104851</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>135711645</v>
       </c>
       <c r="B67" t="n">
-        <v>100940</v>
+        <v>100941</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>135711652</v>
       </c>
       <c r="B68" t="n">
-        <v>100940</v>
+        <v>100941</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>135711689</v>
       </c>
       <c r="B69" t="n">
-        <v>100940</v>
+        <v>100941</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>135711651</v>
       </c>
       <c r="B70" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>135711684</v>
       </c>
       <c r="B71" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 29274-2026 artfynd.xlsx
+++ b/artfynd/A 29274-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ71"/>
+  <dimension ref="A1:AZ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1845,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135711699</v>
+        <v>136583208</v>
       </c>
       <c r="B12" t="n">
-        <v>89318</v>
+        <v>93400</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,34 +1856,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Finnberget, Vb</t>
+          <t>Mensträsk, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>709386</v>
+        <v>709695</v>
       </c>
       <c r="R12" t="n">
-        <v>7220864</v>
+        <v>7220620</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,22 +1910,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,28 +1935,24 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711699</t>
+          <t>https://artportalen.se/Sighting/136583208</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135711701</v>
+        <v>135711699</v>
       </c>
       <c r="B13" t="n">
         <v>89318</v>
@@ -1996,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>709389</v>
+        <v>709386</v>
       </c>
       <c r="R13" t="n">
-        <v>7220902</v>
+        <v>7220864</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2041,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,38 +2062,38 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711701</t>
+          <t>https://artportalen.se/Sighting/135711699</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135711697</v>
+        <v>135711701</v>
       </c>
       <c r="B14" t="n">
-        <v>93058</v>
+        <v>89318</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>4412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2112,10 +2103,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>709373</v>
+        <v>709389</v>
       </c>
       <c r="R14" t="n">
-        <v>7220891</v>
+        <v>7220902</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2147,7 +2138,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2157,7 +2148,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,38 +2178,38 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711697</t>
+          <t>https://artportalen.se/Sighting/135711701</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135711658</v>
+        <v>135711697</v>
       </c>
       <c r="B15" t="n">
-        <v>79460</v>
+        <v>93058</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2228,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>709503</v>
+        <v>709373</v>
       </c>
       <c r="R15" t="n">
-        <v>7220690</v>
+        <v>7220891</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2263,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2273,12 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Bilder</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2308,13 +2294,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711658</t>
+          <t>https://artportalen.se/Sighting/135711697</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135711703</v>
+        <v>135711658</v>
       </c>
       <c r="B16" t="n">
         <v>79460</v>
@@ -2349,10 +2335,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>709458</v>
+        <v>709503</v>
       </c>
       <c r="R16" t="n">
-        <v>7220828</v>
+        <v>7220690</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2384,7 +2370,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2394,7 +2380,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2424,38 +2415,38 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711703</t>
+          <t>https://artportalen.se/Sighting/135711658</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135711704</v>
+        <v>135711703</v>
       </c>
       <c r="B17" t="n">
-        <v>80580</v>
+        <v>79460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2465,10 +2456,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>709451</v>
+        <v>709458</v>
       </c>
       <c r="R17" t="n">
-        <v>7220798</v>
+        <v>7220828</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2500,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2501,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2540,56 +2531,51 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711704</t>
+          <t>https://artportalen.se/Sighting/135711703</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135711686</v>
+        <v>135711704</v>
       </c>
       <c r="B18" t="n">
-        <v>57993</v>
+        <v>80580</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Finnberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>709305</v>
+        <v>709451</v>
       </c>
       <c r="R18" t="n">
-        <v>7220815</v>
+        <v>7220798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2621,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2631,12 +2617,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2666,51 +2647,56 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711686</t>
+          <t>https://artportalen.se/Sighting/135711704</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135711633</v>
+        <v>135711686</v>
       </c>
       <c r="B19" t="n">
-        <v>108353</v>
+        <v>57993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220083</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Finnberget, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>709738</v>
+        <v>709305</v>
       </c>
       <c r="R19" t="n">
-        <v>7220556</v>
+        <v>7220815</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2742,7 +2728,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2752,7 +2738,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2782,13 +2773,13 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711633</t>
+          <t>https://artportalen.se/Sighting/135711686</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135711647</v>
+        <v>135711633</v>
       </c>
       <c r="B20" t="n">
         <v>108353</v>
@@ -2823,10 +2814,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>709571</v>
+        <v>709738</v>
       </c>
       <c r="R20" t="n">
-        <v>7220683</v>
+        <v>7220556</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2858,7 +2849,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2868,7 +2859,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2898,16 +2889,16 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711647</t>
+          <t>https://artportalen.se/Sighting/135711633</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135711631</v>
+        <v>135711647</v>
       </c>
       <c r="B21" t="n">
-        <v>108423</v>
+        <v>108353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,21 +2906,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2939,10 +2930,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>709738</v>
+        <v>709571</v>
       </c>
       <c r="R21" t="n">
-        <v>7220556</v>
+        <v>7220683</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2974,7 +2965,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2984,7 +2975,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3014,13 +3005,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711631</t>
+          <t>https://artportalen.se/Sighting/135711647</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135711649</v>
+        <v>135711631</v>
       </c>
       <c r="B22" t="n">
         <v>108423</v>
@@ -3055,10 +3046,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>709583</v>
+        <v>709738</v>
       </c>
       <c r="R22" t="n">
-        <v>7220703</v>
+        <v>7220556</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,7 +3081,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3100,7 +3091,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3130,13 +3121,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711649</t>
+          <t>https://artportalen.se/Sighting/135711631</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135711653</v>
+        <v>135711649</v>
       </c>
       <c r="B23" t="n">
         <v>108423</v>
@@ -3171,10 +3162,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>709546</v>
+        <v>709583</v>
       </c>
       <c r="R23" t="n">
-        <v>7220699</v>
+        <v>7220703</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3206,7 +3197,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3216,7 +3207,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3246,13 +3237,13 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711653</t>
+          <t>https://artportalen.se/Sighting/135711649</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135711675</v>
+        <v>135711653</v>
       </c>
       <c r="B24" t="n">
         <v>108423</v>
@@ -3287,10 +3278,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>709521</v>
+        <v>709546</v>
       </c>
       <c r="R24" t="n">
-        <v>7220734</v>
+        <v>7220699</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3322,7 +3313,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3332,7 +3323,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3362,13 +3353,13 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711675</t>
+          <t>https://artportalen.se/Sighting/135711653</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135711691</v>
+        <v>135711675</v>
       </c>
       <c r="B25" t="n">
         <v>108423</v>
@@ -3403,10 +3394,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>709321</v>
+        <v>709521</v>
       </c>
       <c r="R25" t="n">
-        <v>7220882</v>
+        <v>7220734</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3438,7 +3429,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3448,7 +3439,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3478,13 +3469,13 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711691</t>
+          <t>https://artportalen.se/Sighting/135711675</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135711708</v>
+        <v>135711691</v>
       </c>
       <c r="B26" t="n">
         <v>108423</v>
@@ -3519,10 +3510,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>709519</v>
+        <v>709321</v>
       </c>
       <c r="R26" t="n">
-        <v>7220740</v>
+        <v>7220882</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3554,7 +3545,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3564,7 +3555,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3594,13 +3585,13 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711708</t>
+          <t>https://artportalen.se/Sighting/135711691</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135711709</v>
+        <v>135711708</v>
       </c>
       <c r="B27" t="n">
         <v>108423</v>
@@ -3635,10 +3626,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>709530</v>
+        <v>709519</v>
       </c>
       <c r="R27" t="n">
-        <v>7220751</v>
+        <v>7220740</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3670,7 +3661,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3680,7 +3671,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3710,38 +3701,38 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711709</t>
+          <t>https://artportalen.se/Sighting/135711708</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135711634</v>
+        <v>135711709</v>
       </c>
       <c r="B28" t="n">
-        <v>99328</v>
+        <v>108423</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3751,10 +3742,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>709604</v>
+        <v>709530</v>
       </c>
       <c r="R28" t="n">
-        <v>7220642</v>
+        <v>7220751</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3786,7 +3777,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3796,7 +3787,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,13 +3817,13 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711634</t>
+          <t>https://artportalen.se/Sighting/135711709</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135711636</v>
+        <v>135711634</v>
       </c>
       <c r="B29" t="n">
         <v>99328</v>
@@ -3867,10 +3858,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>709600</v>
+        <v>709604</v>
       </c>
       <c r="R29" t="n">
-        <v>7220662</v>
+        <v>7220642</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3902,7 +3893,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3912,7 +3903,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3942,13 +3933,13 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711636</t>
+          <t>https://artportalen.se/Sighting/135711634</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135711637</v>
+        <v>135711636</v>
       </c>
       <c r="B30" t="n">
         <v>99328</v>
@@ -3983,10 +3974,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>709575</v>
+        <v>709600</v>
       </c>
       <c r="R30" t="n">
-        <v>7220666</v>
+        <v>7220662</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4018,7 +4009,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4028,12 +4019,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Bild</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4063,13 +4049,13 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711637</t>
+          <t>https://artportalen.se/Sighting/135711636</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135711644</v>
+        <v>135711637</v>
       </c>
       <c r="B31" t="n">
         <v>99328</v>
@@ -4104,10 +4090,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>709561</v>
+        <v>709575</v>
       </c>
       <c r="R31" t="n">
-        <v>7220697</v>
+        <v>7220666</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4139,7 +4125,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4149,7 +4135,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4179,13 +4170,13 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711644</t>
+          <t>https://artportalen.se/Sighting/135711637</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135711656</v>
+        <v>135711644</v>
       </c>
       <c r="B32" t="n">
         <v>99328</v>
@@ -4220,10 +4211,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>709532</v>
+        <v>709561</v>
       </c>
       <c r="R32" t="n">
-        <v>7220667</v>
+        <v>7220697</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4255,7 +4246,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4265,7 +4256,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4295,13 +4286,13 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711656</t>
+          <t>https://artportalen.se/Sighting/135711644</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135711661</v>
+        <v>135711656</v>
       </c>
       <c r="B33" t="n">
         <v>99328</v>
@@ -4336,10 +4327,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>709506</v>
+        <v>709532</v>
       </c>
       <c r="R33" t="n">
-        <v>7220704</v>
+        <v>7220667</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4371,7 +4362,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4381,7 +4372,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4411,13 +4402,13 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711661</t>
+          <t>https://artportalen.se/Sighting/135711656</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135711666</v>
+        <v>135711661</v>
       </c>
       <c r="B34" t="n">
         <v>99328</v>
@@ -4452,10 +4443,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>709508</v>
+        <v>709506</v>
       </c>
       <c r="R34" t="n">
-        <v>7220714</v>
+        <v>7220704</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4487,7 +4478,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4497,7 +4488,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4527,13 +4518,13 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711666</t>
+          <t>https://artportalen.se/Sighting/135711661</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135711670</v>
+        <v>135711666</v>
       </c>
       <c r="B35" t="n">
         <v>99328</v>
@@ -4568,10 +4559,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>709510</v>
+        <v>709508</v>
       </c>
       <c r="R35" t="n">
-        <v>7220711</v>
+        <v>7220714</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4603,7 +4594,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4613,7 +4604,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4643,13 +4634,13 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711670</t>
+          <t>https://artportalen.se/Sighting/135711666</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135711676</v>
+        <v>135711670</v>
       </c>
       <c r="B36" t="n">
         <v>99328</v>
@@ -4684,10 +4675,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>709500</v>
+        <v>709510</v>
       </c>
       <c r="R36" t="n">
-        <v>7220750</v>
+        <v>7220711</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4719,7 +4710,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4729,7 +4720,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4759,13 +4750,13 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711676</t>
+          <t>https://artportalen.se/Sighting/135711670</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135711677</v>
+        <v>135711676</v>
       </c>
       <c r="B37" t="n">
         <v>99328</v>
@@ -4800,10 +4791,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>709503</v>
+        <v>709500</v>
       </c>
       <c r="R37" t="n">
-        <v>7220733</v>
+        <v>7220750</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4835,7 +4826,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4845,7 +4836,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4875,13 +4866,13 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711677</t>
+          <t>https://artportalen.se/Sighting/135711676</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135711678</v>
+        <v>135711677</v>
       </c>
       <c r="B38" t="n">
         <v>99328</v>
@@ -4916,10 +4907,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>709474</v>
+        <v>709503</v>
       </c>
       <c r="R38" t="n">
-        <v>7220731</v>
+        <v>7220733</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4951,7 +4942,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4961,7 +4952,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4991,13 +4982,13 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711678</t>
+          <t>https://artportalen.se/Sighting/135711677</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135711679</v>
+        <v>135711678</v>
       </c>
       <c r="B39" t="n">
         <v>99328</v>
@@ -5032,10 +5023,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>709406</v>
+        <v>709474</v>
       </c>
       <c r="R39" t="n">
-        <v>7220764</v>
+        <v>7220731</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5067,7 +5058,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5077,7 +5068,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5107,13 +5098,13 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711679</t>
+          <t>https://artportalen.se/Sighting/135711678</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135711680</v>
+        <v>135711679</v>
       </c>
       <c r="B40" t="n">
         <v>99328</v>
@@ -5148,10 +5139,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>709383</v>
+        <v>709406</v>
       </c>
       <c r="R40" t="n">
-        <v>7220757</v>
+        <v>7220764</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5183,7 +5174,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5193,7 +5184,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5223,13 +5214,13 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711680</t>
+          <t>https://artportalen.se/Sighting/135711679</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135711681</v>
+        <v>135711680</v>
       </c>
       <c r="B41" t="n">
         <v>99328</v>
@@ -5264,10 +5255,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>709357</v>
+        <v>709383</v>
       </c>
       <c r="R41" t="n">
-        <v>7220788</v>
+        <v>7220757</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5299,7 +5290,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5309,7 +5300,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5339,13 +5330,13 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711681</t>
+          <t>https://artportalen.se/Sighting/135711680</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135711682</v>
+        <v>135711681</v>
       </c>
       <c r="B42" t="n">
         <v>99328</v>
@@ -5380,10 +5371,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>709320</v>
+        <v>709357</v>
       </c>
       <c r="R42" t="n">
-        <v>7220789</v>
+        <v>7220788</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5415,7 +5406,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5425,7 +5416,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5455,13 +5446,13 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711682</t>
+          <t>https://artportalen.se/Sighting/135711681</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135711685</v>
+        <v>135711682</v>
       </c>
       <c r="B43" t="n">
         <v>99328</v>
@@ -5496,10 +5487,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>709305</v>
+        <v>709320</v>
       </c>
       <c r="R43" t="n">
-        <v>7220815</v>
+        <v>7220789</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5531,7 +5522,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5541,7 +5532,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5571,13 +5562,13 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711685</t>
+          <t>https://artportalen.se/Sighting/135711682</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135711692</v>
+        <v>135711685</v>
       </c>
       <c r="B44" t="n">
         <v>99328</v>
@@ -5612,10 +5603,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>709336</v>
+        <v>709305</v>
       </c>
       <c r="R44" t="n">
-        <v>7220886</v>
+        <v>7220815</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5647,7 +5638,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5657,7 +5648,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5687,13 +5678,13 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711692</t>
+          <t>https://artportalen.se/Sighting/135711685</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135711693</v>
+        <v>135711692</v>
       </c>
       <c r="B45" t="n">
         <v>99328</v>
@@ -5728,10 +5719,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>709345</v>
+        <v>709336</v>
       </c>
       <c r="R45" t="n">
-        <v>7220884</v>
+        <v>7220886</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5763,7 +5754,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5773,7 +5764,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5803,13 +5794,13 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711693</t>
+          <t>https://artportalen.se/Sighting/135711692</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135711698</v>
+        <v>135711693</v>
       </c>
       <c r="B46" t="n">
         <v>99328</v>
@@ -5844,10 +5835,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>709387</v>
+        <v>709345</v>
       </c>
       <c r="R46" t="n">
-        <v>7220894</v>
+        <v>7220884</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5879,7 +5870,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5889,7 +5880,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5919,13 +5910,13 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711698</t>
+          <t>https://artportalen.se/Sighting/135711693</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135711700</v>
+        <v>135711698</v>
       </c>
       <c r="B47" t="n">
         <v>99328</v>
@@ -5960,10 +5951,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>709386</v>
+        <v>709387</v>
       </c>
       <c r="R47" t="n">
-        <v>7220864</v>
+        <v>7220894</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5995,7 +5986,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6005,7 +5996,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6035,13 +6026,13 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711700</t>
+          <t>https://artportalen.se/Sighting/135711698</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135711702</v>
+        <v>135711700</v>
       </c>
       <c r="B48" t="n">
         <v>99328</v>
@@ -6076,10 +6067,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>709425</v>
+        <v>709386</v>
       </c>
       <c r="R48" t="n">
-        <v>7220904</v>
+        <v>7220864</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6111,7 +6102,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6121,7 +6112,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6151,13 +6142,13 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711702</t>
+          <t>https://artportalen.se/Sighting/135711700</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135711707</v>
+        <v>135711702</v>
       </c>
       <c r="B49" t="n">
         <v>99328</v>
@@ -6192,10 +6183,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>709512</v>
+        <v>709425</v>
       </c>
       <c r="R49" t="n">
-        <v>7220741</v>
+        <v>7220904</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6227,7 +6218,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6237,7 +6228,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6267,38 +6258,38 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711707</t>
+          <t>https://artportalen.se/Sighting/135711702</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135711640</v>
+        <v>135711707</v>
       </c>
       <c r="B50" t="n">
-        <v>99350</v>
+        <v>99328</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6308,10 +6299,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>709551</v>
+        <v>709512</v>
       </c>
       <c r="R50" t="n">
-        <v>7220687</v>
+        <v>7220741</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6343,7 +6334,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6353,7 +6344,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6383,13 +6374,13 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711640</t>
+          <t>https://artportalen.se/Sighting/135711707</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135711657</v>
+        <v>135711640</v>
       </c>
       <c r="B51" t="n">
         <v>99350</v>
@@ -6424,10 +6415,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>709533</v>
+        <v>709551</v>
       </c>
       <c r="R51" t="n">
-        <v>7220667</v>
+        <v>7220687</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6459,7 +6450,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6469,7 +6460,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6499,13 +6490,13 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711657</t>
+          <t>https://artportalen.se/Sighting/135711640</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135711683</v>
+        <v>135711657</v>
       </c>
       <c r="B52" t="n">
         <v>99350</v>
@@ -6540,10 +6531,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>709303</v>
+        <v>709533</v>
       </c>
       <c r="R52" t="n">
-        <v>7220807</v>
+        <v>7220667</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6575,7 +6566,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6585,7 +6576,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6615,13 +6606,13 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711683</t>
+          <t>https://artportalen.se/Sighting/135711657</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135711705</v>
+        <v>135711683</v>
       </c>
       <c r="B53" t="n">
         <v>99350</v>
@@ -6656,10 +6647,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>709487</v>
+        <v>709303</v>
       </c>
       <c r="R53" t="n">
-        <v>7220763</v>
+        <v>7220807</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6691,7 +6682,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6701,7 +6692,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6731,16 +6722,16 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711705</t>
+          <t>https://artportalen.se/Sighting/135711683</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135711639</v>
+        <v>135711705</v>
       </c>
       <c r="B54" t="n">
-        <v>104851</v>
+        <v>99350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6748,21 +6739,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222412</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6772,10 +6763,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>709558</v>
+        <v>709487</v>
       </c>
       <c r="R54" t="n">
-        <v>7220679</v>
+        <v>7220763</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6807,7 +6798,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6817,12 +6808,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Bild</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6852,13 +6838,13 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711639</t>
+          <t>https://artportalen.se/Sighting/135711705</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135711641</v>
+        <v>135711639</v>
       </c>
       <c r="B55" t="n">
         <v>104851</v>
@@ -6893,10 +6879,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>709546</v>
+        <v>709558</v>
       </c>
       <c r="R55" t="n">
-        <v>7220675</v>
+        <v>7220679</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6928,7 +6914,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6938,7 +6924,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6968,13 +6959,13 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711641</t>
+          <t>https://artportalen.se/Sighting/135711639</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135711642</v>
+        <v>135711641</v>
       </c>
       <c r="B56" t="n">
         <v>104851</v>
@@ -7009,10 +7000,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>709561</v>
+        <v>709546</v>
       </c>
       <c r="R56" t="n">
-        <v>7220689</v>
+        <v>7220675</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7044,7 +7035,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7054,7 +7045,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7084,13 +7075,13 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711642</t>
+          <t>https://artportalen.se/Sighting/135711641</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135711646</v>
+        <v>135711642</v>
       </c>
       <c r="B57" t="n">
         <v>104851</v>
@@ -7125,10 +7116,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>709571</v>
+        <v>709561</v>
       </c>
       <c r="R57" t="n">
-        <v>7220683</v>
+        <v>7220689</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7160,7 +7151,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7170,7 +7161,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7200,13 +7191,13 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711646</t>
+          <t>https://artportalen.se/Sighting/135711642</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135711648</v>
+        <v>135711646</v>
       </c>
       <c r="B58" t="n">
         <v>104851</v>
@@ -7241,10 +7232,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>709567</v>
+        <v>709571</v>
       </c>
       <c r="R58" t="n">
-        <v>7220695</v>
+        <v>7220683</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7276,7 +7267,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7286,7 +7277,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7316,13 +7307,13 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711648</t>
+          <t>https://artportalen.se/Sighting/135711646</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135711650</v>
+        <v>135711648</v>
       </c>
       <c r="B59" t="n">
         <v>104851</v>
@@ -7357,10 +7348,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>709577</v>
+        <v>709567</v>
       </c>
       <c r="R59" t="n">
-        <v>7220700</v>
+        <v>7220695</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7392,7 +7383,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7402,7 +7393,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7432,13 +7423,13 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711650</t>
+          <t>https://artportalen.se/Sighting/135711648</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135711660</v>
+        <v>135711650</v>
       </c>
       <c r="B60" t="n">
         <v>104851</v>
@@ -7473,10 +7464,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>709501</v>
+        <v>709577</v>
       </c>
       <c r="R60" t="n">
-        <v>7220705</v>
+        <v>7220700</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7508,7 +7499,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7518,7 +7509,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7548,13 +7539,13 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711660</t>
+          <t>https://artportalen.se/Sighting/135711650</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135711664</v>
+        <v>135711660</v>
       </c>
       <c r="B61" t="n">
         <v>104851</v>
@@ -7589,10 +7580,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>709499</v>
+        <v>709501</v>
       </c>
       <c r="R61" t="n">
-        <v>7220709</v>
+        <v>7220705</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7624,7 +7615,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7634,7 +7625,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7664,13 +7655,13 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711664</t>
+          <t>https://artportalen.se/Sighting/135711660</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135711674</v>
+        <v>135711664</v>
       </c>
       <c r="B62" t="n">
         <v>104851</v>
@@ -7705,10 +7696,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>709521</v>
+        <v>709499</v>
       </c>
       <c r="R62" t="n">
-        <v>7220734</v>
+        <v>7220709</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7740,7 +7731,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7750,7 +7741,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7780,13 +7771,13 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711674</t>
+          <t>https://artportalen.se/Sighting/135711664</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135711694</v>
+        <v>135711674</v>
       </c>
       <c r="B63" t="n">
         <v>104851</v>
@@ -7821,10 +7812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>709355</v>
+        <v>709521</v>
       </c>
       <c r="R63" t="n">
-        <v>7220873</v>
+        <v>7220734</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7856,7 +7847,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7866,12 +7857,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Bild</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7901,13 +7887,13 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711694</t>
+          <t>https://artportalen.se/Sighting/135711674</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135711695</v>
+        <v>135711694</v>
       </c>
       <c r="B64" t="n">
         <v>104851</v>
@@ -7942,10 +7928,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>709359</v>
+        <v>709355</v>
       </c>
       <c r="R64" t="n">
-        <v>7220889</v>
+        <v>7220873</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7977,7 +7963,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7987,12 +7973,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Flera plantor</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8022,13 +8008,13 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711695</t>
+          <t>https://artportalen.se/Sighting/135711694</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135711696</v>
+        <v>135711695</v>
       </c>
       <c r="B65" t="n">
         <v>104851</v>
@@ -8063,10 +8049,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>709366</v>
+        <v>709359</v>
       </c>
       <c r="R65" t="n">
-        <v>7220879</v>
+        <v>7220889</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8098,7 +8084,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8108,7 +8094,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Flera plantor</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8138,13 +8129,13 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711696</t>
+          <t>https://artportalen.se/Sighting/135711695</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135711711</v>
+        <v>135711696</v>
       </c>
       <c r="B66" t="n">
         <v>104851</v>
@@ -8179,10 +8170,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>709545</v>
+        <v>709366</v>
       </c>
       <c r="R66" t="n">
-        <v>7220781</v>
+        <v>7220879</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8214,7 +8205,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8224,7 +8215,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8254,16 +8245,16 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711711</t>
+          <t>https://artportalen.se/Sighting/135711696</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135711645</v>
+        <v>135711711</v>
       </c>
       <c r="B67" t="n">
-        <v>100941</v>
+        <v>104851</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8271,16 +8262,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222584</v>
+        <v>222412</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8295,10 +8286,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>709561</v>
+        <v>709545</v>
       </c>
       <c r="R67" t="n">
-        <v>7220697</v>
+        <v>7220781</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8330,7 +8321,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8340,7 +8331,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8370,16 +8361,16 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711645</t>
+          <t>https://artportalen.se/Sighting/135711711</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135711652</v>
+        <v>136583209</v>
       </c>
       <c r="B68" t="n">
-        <v>100941</v>
+        <v>100368</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8387,34 +8378,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222584</v>
+        <v>222467</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Finnberget, Vb</t>
+          <t>Mensträsk, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>709546</v>
+        <v>709711</v>
       </c>
       <c r="R68" t="n">
-        <v>7220699</v>
+        <v>7220591</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8441,22 +8432,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8471,31 +8457,27 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711652</t>
+          <t>https://artportalen.se/Sighting/136583209</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135711689</v>
+        <v>136583210</v>
       </c>
       <c r="B69" t="n">
-        <v>100941</v>
+        <v>100368</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8503,34 +8485,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222584</v>
+        <v>222467</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Finnberget, Vb</t>
+          <t>Mensträsk, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>709308</v>
+        <v>709747</v>
       </c>
       <c r="R69" t="n">
-        <v>7220872</v>
+        <v>7220554</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8557,22 +8539,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>16:08</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>16:08</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8587,31 +8564,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711689</t>
+          <t>https://artportalen.se/Sighting/136583210</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135711651</v>
+        <v>135711645</v>
       </c>
       <c r="B70" t="n">
-        <v>99134</v>
+        <v>100941</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8619,16 +8592,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>223049</v>
+        <v>222584</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8643,10 +8616,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>709546</v>
+        <v>709561</v>
       </c>
       <c r="R70" t="n">
-        <v>7220699</v>
+        <v>7220697</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8678,7 +8651,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8688,7 +8661,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8718,16 +8691,16 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135711651</t>
+          <t>https://artportalen.se/Sighting/135711645</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135711684</v>
+        <v>135711652</v>
       </c>
       <c r="B71" t="n">
-        <v>99134</v>
+        <v>100941</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8735,16 +8708,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>223049</v>
+        <v>222584</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8759,10 +8732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>709303</v>
+        <v>709546</v>
       </c>
       <c r="R71" t="n">
-        <v>7220807</v>
+        <v>7220699</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8794,7 +8767,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8804,7 +8777,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8833,6 +8806,354 @@
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135711652</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135711689</v>
+      </c>
+      <c r="B72" t="n">
+        <v>100941</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Finnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>709308</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7220872</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135711689</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135711651</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99134</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Finnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>709546</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7220699</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135711651</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135711684</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99134</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Finnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>709303</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7220807</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135711684</t>
         </is>
@@ -8910,6 +9231,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
